--- a/public/documentation/assessment/Portfolio_Assessment_Executive_Summary.xlsx
+++ b/public/documentation/assessment/Portfolio_Assessment_Executive_Summary.xlsx
@@ -4,8 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Portfolio Overview" sheetId="1" r:id="rId1"/>
-    <sheet name="Business Areas" sheetId="2" r:id="rId2"/>
-    <sheet name="Technology Landscape" sheetId="3" r:id="rId3"/>
+    <sheet name="Asset Inventory" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -417,7 +416,7 @@
         <v>Total Discovered Assets</v>
       </c>
       <c r="B2">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C2" t="str">
         <v>Portfolio Scope</v>
@@ -428,7 +427,7 @@
         <v>BI Dashboards &amp; Reports</v>
       </c>
       <c r="B3">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C3" t="str">
         <v>Portfolio Scope</v>
@@ -450,7 +449,7 @@
         <v>Business Areas Covered</v>
       </c>
       <c r="B5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" t="str">
         <v>Business Coverage</v>
@@ -461,7 +460,7 @@
         <v>Connected Data Sources</v>
       </c>
       <c r="B6">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C6" t="str">
         <v>Architecture</v>
@@ -472,7 +471,7 @@
         <v>Downstream Data Targets</v>
       </c>
       <c r="B7">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C7" t="str">
         <v>Architecture</v>
@@ -483,7 +482,7 @@
         <v>Active Business KPIs</v>
       </c>
       <c r="B8">
-        <v>148</v>
+        <v>414</v>
       </c>
       <c r="C8" t="str">
         <v>Metrics</v>
@@ -491,13 +490,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Estimated Redundancy Rate</v>
-      </c>
-      <c r="B9" t="str">
-        <v>38%</v>
+        <v>Calculated Fields &amp; DAX</v>
+      </c>
+      <c r="B9">
+        <v>564</v>
       </c>
       <c r="C9" t="str">
-        <v>Opportunity</v>
+        <v>Business Logic</v>
       </c>
     </row>
   </sheetData>
@@ -509,281 +508,996 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:L32"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>Asset ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Asset Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Technology</v>
+      </c>
+      <c r="D1" t="str">
         <v>Business Area</v>
       </c>
-      <c r="B1" t="str">
-        <v>Asset Count</v>
-      </c>
-      <c r="C1" t="str">
-        <v>BI Count</v>
-      </c>
-      <c r="D1" t="str">
-        <v>ETL Count</v>
-      </c>
       <c r="E1" t="str">
-        <v>Primary Tech</v>
+        <v>Asset Type</v>
       </c>
       <c r="F1" t="str">
-        <v>Data Complexity</v>
+        <v>Owner</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Data Sources</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Data Targets</v>
+      </c>
+      <c r="I1" t="str">
+        <v>KPI Count</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Complexity</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Criticality</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Tool Count</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>c1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Claims - Executive Summary</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Tableau</v>
+      </c>
+      <c r="D2" t="str">
         <v>Claims</v>
       </c>
-      <c r="B2">
-        <v>15</v>
-      </c>
-      <c r="C2">
-        <v>9</v>
-      </c>
-      <c r="D2">
-        <v>6</v>
-      </c>
       <c r="E2" t="str">
-        <v>Tableau / Alteryx</v>
+        <v>Dashboard</v>
       </c>
       <c r="F2" t="str">
-        <v>High</v>
+        <v>EXLService</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Underwriting</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
+        <v>c2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Claims - State Performance</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Tableau</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Claims</v>
       </c>
       <c r="E3" t="str">
-        <v>Power BI / Tableau</v>
+        <v>Dashboard</v>
       </c>
       <c r="F3" t="str">
-        <v>Medium</v>
+        <v>EXLService</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Distribution</v>
-      </c>
-      <c r="B4">
+        <v>c3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>P&amp;C Claims Dashboard v3</v>
+      </c>
+      <c r="C4" t="str">
+        <v>MicroStrategy</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Claims</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="F4" t="str">
+        <v>EXLService</v>
+      </c>
+      <c r="G4">
         <v>6</v>
       </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Power BI / Tableau</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Medium</v>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Policy Administration</v>
-      </c>
-      <c r="B5">
+        <v>c4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Healthcare Claim Analysis Dashboard</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Tableau</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Claims</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="F5" t="str">
+        <v>EXLService</v>
+      </c>
+      <c r="G5">
         <v>2</v>
       </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Tableau / Power BI</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Low</v>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Finance</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
+        <v>u3</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Loss Ratio</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Power BI</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Claims</v>
       </c>
       <c r="E6" t="str">
-        <v>Power BI / Tableau</v>
+        <v>Dashboard</v>
       </c>
       <c r="F6" t="str">
-        <v>High</v>
+        <v>EXL</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
+        <v>u1</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Car Insurance Dashboard</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Tableau</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Underwriting</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="F7" t="str">
+        <v>EXL</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>u2</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Motor Insurance Dashboard</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Tableau</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Underwriting</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="F8" t="str">
+        <v>EXL</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>u6</v>
+      </c>
+      <c r="B9" t="str">
+        <v>FFQ_Test</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Power BI</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Underwriting</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="F9" t="str">
+        <v>EXL</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>d1</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Claims - Agent Performance</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Tableau</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Distribution</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="F10" t="str">
+        <v>EXLDistribution</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>d2</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Cross Sell Dashboard</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Tableau</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Distribution</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="F11" t="str">
+        <v>EXLDistribution</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>d7</v>
+      </c>
+      <c r="B12" t="str">
+        <v>INSURANCE ANALYTICS DASHBOARD</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Tableau</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Distribution</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="F12" t="str">
+        <v>EXLDistribution</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>d3</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Jornaya Dashboard PBI</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Power BI</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Distribution</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="F13" t="str">
+        <v>EXLDistribution</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>d4</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Revenue Opportunities</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Power BI</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Distribution</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="F14" t="str">
+        <v>EXLDistribution</v>
+      </c>
+      <c r="G14">
+        <v>6</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>d5</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Bottom 25% Agents</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Power BI</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Distribution</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="F15" t="str">
+        <v>EXLDistribution</v>
+      </c>
+      <c r="G15">
+        <v>3</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>d8</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Cross_Sell_dashboardpbip</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Power BI</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Distribution</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="F16" t="str">
+        <v>EXLDistribution</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>d9</v>
+      </c>
+      <c r="B17" t="str">
+        <v>New Business (Bottom 25% agents)</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Power BI</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Distribution</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="F17" t="str">
+        <v>EXL_S</v>
+      </c>
+      <c r="G17">
+        <v>6</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>d10</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Insurance_Analytics_Dashboard</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Power BI</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Distribution</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="F18" t="str">
+        <v>EXL_S</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>p1</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Survival Rate</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Power BI</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Policy Administration</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="F19" t="str">
+        <v>EXLPolicy</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>f1</v>
+      </c>
+      <c r="B20" t="str">
+        <v>IT Spend Analysis Sample PBIX</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Power BI</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="F20" t="str">
+        <v>EXL_IT</v>
+      </c>
+      <c r="G20">
+        <v>8</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>f2</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Store Sales</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Power BI</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="F21" t="str">
+        <v>EXL_Finance</v>
+      </c>
+      <c r="G21">
+        <v>4</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>f3</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Sales &amp; Returns Sample v3</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Power BI</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="F22" t="str">
+        <v>EXL_Services</v>
+      </c>
+      <c r="G22">
+        <v>13</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>cu1</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Benefeciery services_v1</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Tableau</v>
+      </c>
+      <c r="D23" t="str">
         <v>Customer</v>
       </c>
-      <c r="B7">
+      <c r="E23" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="F23" t="str">
+        <v>EXL_Beneficiaries</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>cu2</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Benefeciery_services_Aging_Dashboard</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Tableau</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Customer</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="F24" t="str">
+        <v>EXL_Beneficiaries_Aging</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>c10</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Claims_Extract_Volume</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Alteryx</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Claims</v>
+      </c>
+      <c r="E25" t="str">
+        <v>ETL Workflow</v>
+      </c>
+      <c r="F25" t="str">
+        <v>EXLService</v>
+      </c>
+      <c r="G25">
+        <v>4</v>
+      </c>
+      <c r="H25">
+        <v>5</v>
+      </c>
+      <c r="J25" t="str">
+        <v>High</v>
+      </c>
+      <c r="K25" t="str">
+        <v>High</v>
+      </c>
+      <c r="L25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>c11</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Workflow_03</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Alteryx</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Claims</v>
+      </c>
+      <c r="E26" t="str">
+        <v>ETL Workflow</v>
+      </c>
+      <c r="F26" t="str">
+        <v>EXLService</v>
+      </c>
+      <c r="G26">
+        <v>5</v>
+      </c>
+      <c r="H26">
         <v>3</v>
       </c>
-      <c r="C7">
+      <c r="J26" t="str">
+        <v>High</v>
+      </c>
+      <c r="K26" t="str">
+        <v>High</v>
+      </c>
+      <c r="L26">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>c12</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Workflow_01</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Alteryx</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Claims</v>
+      </c>
+      <c r="E27" t="str">
+        <v>ETL Workflow</v>
+      </c>
+      <c r="F27" t="str">
+        <v>EXLService</v>
+      </c>
+      <c r="G27">
         <v>3</v>
       </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Tableau / Power BI</v>
-      </c>
-      <c r="F7" t="str">
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="J27" t="str">
         <v>Medium</v>
+      </c>
+      <c r="K27" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="L27">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>c13</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Workflow_02</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Alteryx</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Claims</v>
+      </c>
+      <c r="E28" t="str">
+        <v>ETL Workflow</v>
+      </c>
+      <c r="F28" t="str">
+        <v>EXLService</v>
+      </c>
+      <c r="G28">
+        <v>3</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="J28" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="L28">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>c14</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Claims_Extract_Volume_v2</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Alteryx</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Claims</v>
+      </c>
+      <c r="E29" t="str">
+        <v>ETL Workflow</v>
+      </c>
+      <c r="F29" t="str">
+        <v>EXLService</v>
+      </c>
+      <c r="G29">
+        <v>4</v>
+      </c>
+      <c r="H29">
+        <v>5</v>
+      </c>
+      <c r="J29" t="str">
+        <v>High</v>
+      </c>
+      <c r="K29" t="str">
+        <v>High</v>
+      </c>
+      <c r="L29">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>c15</v>
+      </c>
+      <c r="B30" t="str">
+        <v>claims_processing</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Python</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Claims</v>
+      </c>
+      <c r="E30" t="str">
+        <v>ETL Workflow</v>
+      </c>
+      <c r="F30" t="str">
+        <v>EXLService</v>
+      </c>
+      <c r="G30">
+        <v>4</v>
+      </c>
+      <c r="H30">
+        <v>5</v>
+      </c>
+      <c r="J30" t="str">
+        <v>High</v>
+      </c>
+      <c r="K30" t="str">
+        <v>High</v>
+      </c>
+      <c r="L30">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>u4</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Workflow_04</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Alteryx</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Underwriting</v>
+      </c>
+      <c r="E31" t="str">
+        <v>ETL Workflow</v>
+      </c>
+      <c r="F31" t="str">
+        <v>EXLService</v>
+      </c>
+      <c r="G31">
+        <v>7</v>
+      </c>
+      <c r="H31">
+        <v>3</v>
+      </c>
+      <c r="J31" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K31" t="str">
+        <v>Low</v>
+      </c>
+      <c r="L31">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>d6</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Workflow_08</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Alteryx</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Distribution</v>
+      </c>
+      <c r="E32" t="str">
+        <v>ETL Workflow</v>
+      </c>
+      <c r="F32" t="str">
+        <v>EXLService</v>
+      </c>
+      <c r="G32">
+        <v>5</v>
+      </c>
+      <c r="H32">
+        <v>3</v>
+      </c>
+      <c r="J32" t="str">
+        <v>Low</v>
+      </c>
+      <c r="K32" t="str">
+        <v>Low</v>
+      </c>
+      <c r="L32">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Technology</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Domain</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Asset Count</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Health Score</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Modernization Status</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Tableau</v>
-      </c>
-      <c r="B2" t="str">
-        <v>BI</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
-      </c>
-      <c r="D2" t="str">
-        <v>88/100</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Candidate for Consolidation</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Power BI</v>
-      </c>
-      <c r="B3" t="str">
-        <v>BI</v>
-      </c>
-      <c r="C3">
-        <v>9</v>
-      </c>
-      <c r="D3" t="str">
-        <v>92/100</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Strategic Target Platform</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>MicroStrategy</v>
-      </c>
-      <c r="B4" t="str">
-        <v>BI</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4" t="str">
-        <v>45/100</v>
-      </c>
-      <c r="E4" t="str">
-        <v>High Priority Migration</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>ThoughtSpot</v>
-      </c>
-      <c r="B5" t="str">
-        <v>BI</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" t="str">
-        <v>95/100</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Modern Self-Service Target</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Alteryx</v>
-      </c>
-      <c r="B6" t="str">
-        <v>ETL</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-      <c r="D6" t="str">
-        <v>74/100</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Candidate for Cloud Migration</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Python</v>
-      </c>
-      <c r="B7" t="str">
-        <v>ETL</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7" t="str">
-        <v>90/100</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Strategic Modern Codebase</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L32"/>
   </ignoredErrors>
 </worksheet>
 </file>